--- a/ig/ch-term/ValueSet-DocumentEntry.eventCodeList.xlsx
+++ b/ig/ch-term/ValueSet-DocumentEntry.eventCodeList.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-01T16:04:34+01:00</t>
+    <t>2025-12-01T16:04:34+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,6 +111,12 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>BI</t>
+  </si>
+  <si>
+    <t>Biomagnetic Imaging</t>
+  </si>
+  <si>
     <t>TG</t>
   </si>
   <si>
@@ -183,202 +189,202 @@
     <t>Confocal Microscopy</t>
   </si>
   <si>
+    <t>OPTENF</t>
+  </si>
+  <si>
+    <t>Ophthalmic Tomography En Face</t>
+  </si>
+  <si>
+    <t>OPTBSV</t>
+  </si>
+  <si>
+    <t>Ophthalmic Tomography B-scan Volume Analysis</t>
+  </si>
+  <si>
+    <t>OPV</t>
+  </si>
+  <si>
+    <t>Ophthalmic Visual Field</t>
+  </si>
+  <si>
+    <t>DX</t>
+  </si>
+  <si>
+    <t>Digital Radiography</t>
+  </si>
+  <si>
+    <t>OPT</t>
+  </si>
+  <si>
+    <t>Ophthalmic Tomography</t>
+  </si>
+  <si>
+    <t>BMD</t>
+  </si>
+  <si>
+    <t>Bone Mineral Densitometry</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>Mammography</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Slide Microscopy</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Ultrasound</t>
+  </si>
+  <si>
+    <t>OP</t>
+  </si>
+  <si>
+    <t>Ophthalmic Photography</t>
+  </si>
+  <si>
+    <t>IVOCT</t>
+  </si>
+  <si>
+    <t>Intravascular Optical Coherence Tomography</t>
+  </si>
+  <si>
+    <t>MR</t>
+  </si>
+  <si>
+    <t>Magnetic Resonance</t>
+  </si>
+  <si>
+    <t>ECG</t>
+  </si>
+  <si>
+    <t>Electrocardiography</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>General Microscopy</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>Intra-oral Radiography</t>
+  </si>
+  <si>
+    <t>XA</t>
+  </si>
+  <si>
+    <t>X-Ray Angiography</t>
+  </si>
+  <si>
+    <t>XC</t>
+  </si>
+  <si>
+    <t>External-camera Photography</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>Visual Acuity</t>
+  </si>
+  <si>
+    <t>IVUS</t>
+  </si>
+  <si>
+    <t>Intravascular Ultrasound</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>Computed Radiography</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>Endoscopy</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Autorefraction</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Computed Tomography</t>
+  </si>
+  <si>
+    <t>OSS</t>
+  </si>
+  <si>
+    <t>Optical Surface Scanner</t>
+  </si>
+  <si>
+    <t>LEN</t>
+  </si>
+  <si>
+    <t>Lensometry</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>Radiographic imaging</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>Radiofluoroscopy</t>
+  </si>
+  <si>
+    <t>KER</t>
+  </si>
+  <si>
+    <t>Keratometry</t>
+  </si>
+  <si>
+    <t>HD</t>
+  </si>
+  <si>
+    <t>Hemodynamic Waveform</t>
+  </si>
+  <si>
+    <t>OAM</t>
+  </si>
+  <si>
+    <t>Ophthalmic Axial Measurements</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>Nuclear Medicine</t>
+  </si>
+  <si>
+    <t>OCT</t>
+  </si>
+  <si>
+    <t>Optical Coherence Tomography</t>
+  </si>
+  <si>
     <t>BDUS</t>
   </si>
   <si>
     <t>Ultrasound Bone Densitometry</t>
-  </si>
-  <si>
-    <t>OPTENF</t>
-  </si>
-  <si>
-    <t>Ophthalmic Tomography En Face</t>
-  </si>
-  <si>
-    <t>OPTBSV</t>
-  </si>
-  <si>
-    <t>Ophthalmic Tomography B-scan Volume Analysis</t>
-  </si>
-  <si>
-    <t>OPV</t>
-  </si>
-  <si>
-    <t>Ophthalmic Visual Field</t>
-  </si>
-  <si>
-    <t>DX</t>
-  </si>
-  <si>
-    <t>Digital Radiography</t>
-  </si>
-  <si>
-    <t>OPT</t>
-  </si>
-  <si>
-    <t>Ophthalmic Tomography</t>
-  </si>
-  <si>
-    <t>BMD</t>
-  </si>
-  <si>
-    <t>Bone Mineral Densitometry</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>Mammography</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>Slide Microscopy</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>Ultrasound</t>
-  </si>
-  <si>
-    <t>OP</t>
-  </si>
-  <si>
-    <t>Ophthalmic Photography</t>
-  </si>
-  <si>
-    <t>IVOCT</t>
-  </si>
-  <si>
-    <t>Intravascular Optical Coherence Tomography</t>
-  </si>
-  <si>
-    <t>MR</t>
-  </si>
-  <si>
-    <t>Magnetic Resonance</t>
-  </si>
-  <si>
-    <t>ECG</t>
-  </si>
-  <si>
-    <t>Electrocardiography</t>
-  </si>
-  <si>
-    <t>GM</t>
-  </si>
-  <si>
-    <t>General Microscopy</t>
-  </si>
-  <si>
-    <t>IO</t>
-  </si>
-  <si>
-    <t>Intra-oral Radiography</t>
-  </si>
-  <si>
-    <t>XA</t>
-  </si>
-  <si>
-    <t>X-Ray Angiography</t>
-  </si>
-  <si>
-    <t>XC</t>
-  </si>
-  <si>
-    <t>External-camera Photography</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>Visual Acuity</t>
-  </si>
-  <si>
-    <t>IVUS</t>
-  </si>
-  <si>
-    <t>Intravascular Ultrasound</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>Computed Radiography</t>
-  </si>
-  <si>
-    <t>ES</t>
-  </si>
-  <si>
-    <t>Endoscopy</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>Autorefraction</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>Computed Tomography</t>
-  </si>
-  <si>
-    <t>OSS</t>
-  </si>
-  <si>
-    <t>Optical Surface Scanner</t>
-  </si>
-  <si>
-    <t>LEN</t>
-  </si>
-  <si>
-    <t>Lensometry</t>
-  </si>
-  <si>
-    <t>RG</t>
-  </si>
-  <si>
-    <t>Radiographic imaging</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>Radiofluoroscopy</t>
-  </si>
-  <si>
-    <t>KER</t>
-  </si>
-  <si>
-    <t>Keratometry</t>
-  </si>
-  <si>
-    <t>HD</t>
-  </si>
-  <si>
-    <t>Hemodynamic Waveform</t>
-  </si>
-  <si>
-    <t>OAM</t>
-  </si>
-  <si>
-    <t>Ophthalmic Axial Measurements</t>
-  </si>
-  <si>
-    <t>NM</t>
-  </si>
-  <si>
-    <t>Nuclear Medicine</t>
-  </si>
-  <si>
-    <t>OCT</t>
-  </si>
-  <si>
-    <t>Optical Coherence Tomography</t>
   </si>
   <si>
     <t>PT</t>
@@ -1082,74 +1088,74 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
